--- a/src/result/olivetti/result_cross_validation.xlsx
+++ b/src/result/olivetti/result_cross_validation.xlsx
@@ -413,101 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="n">
+      <c r="A1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mean_accuracy</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>std_accuracy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
         <v>0.02788866755113583</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>confidence_interval inf</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="n">
         <v>0.860889331564395</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>confidence_interval sup</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" t="n">
         <v>0.9724440017689383</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>score_1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>score_2</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" t="n">
         <v>0.8833333333333333</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>score_3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>score_4</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>score_5</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" t="n">
         <v>0.95</v>
       </c>
     </row>
